--- a/noboribata-lp/docs/後藤染工_ご確認事項シート_20261027.xlsx
+++ b/noboribata-lp/docs/後藤染工_ご確認事項シート_20261027.xlsx
@@ -28,7 +28,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="198">
   <si>
-    <t xml:space="preserve">のぼり旗の外注パートナー（新ページ）ご確認事項シート</t>
+    <t xml:space="preserve">のぼり旗の量産・外注パートナー（新ページ）ご確認事項シート</t>
   </si>
   <si>
     <t xml:space="preserve">株式会社後藤染工 御中</t>
